--- a/data/trans_camb/Hacinamiento_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,16</t>
+          <t>-1,03; 3,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,53</t>
+          <t>-1,18; 3,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 1,02</t>
+          <t>-3,65; 1,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 1,11</t>
+          <t>-3,34; 1,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,0</t>
+          <t>-3,68; 0,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,68; -1,85</t>
+          <t>-5,82; -1,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,76</t>
+          <t>-1,71; 1,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,58</t>
+          <t>-1,55; 1,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -1,24</t>
+          <t>-4,26; -1,28</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 135,37</t>
+          <t>-24,39; 134,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 130,62</t>
+          <t>-27,86; 139,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-83,35; 74,49</t>
+          <t>-85,1; 71,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 28,59</t>
+          <t>-51,08; 34,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,4; 22,47</t>
+          <t>-55,4; 22,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,18; -45,41</t>
+          <t>-84,77; -44,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 49,95</t>
+          <t>-33,04; 42,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 43,87</t>
+          <t>-29,29; 47,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-78,66; -25,31</t>
+          <t>-80,11; -23,92</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,61</t>
+          <t>-3,61; 0,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; -0,26</t>
+          <t>-4,22; -0,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,14; -2,5</t>
+          <t>-6,54; -2,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 1,69</t>
+          <t>-2,98; 1,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; -0,49</t>
+          <t>-4,61; -0,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -2,55</t>
+          <t>-6,55; -2,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,57</t>
+          <t>-2,41; 0,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; -1,04</t>
+          <t>-3,73; -0,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,69; -2,93</t>
+          <t>-5,64; -3,03</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,71; 14,15</t>
+          <t>-49,76; 16,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,82; -4,25</t>
+          <t>-60,29; -6,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-86,88; -49,28</t>
+          <t>-87,47; -46,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,42; 32,08</t>
+          <t>-36,75; 39,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,7; -8,03</t>
+          <t>-59,42; -9,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,1; -46,38</t>
+          <t>-80,43; -45,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 11,05</t>
+          <t>-34,75; 11,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,2; -18,51</t>
+          <t>-54,03; -12,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-81,22; -54,29</t>
+          <t>-80,99; -54,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,79</t>
+          <t>0,16; 4,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,77</t>
+          <t>-0,0; 4,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 1,33</t>
+          <t>-2,55; 1,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 6,47</t>
+          <t>1,06; 6,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,33</t>
+          <t>-1,97; 3,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,45; -0,18</t>
+          <t>-5,51; -0,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,89</t>
+          <t>1,12; 4,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,42</t>
+          <t>-0,07; 3,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 0,14</t>
+          <t>-3,35; 0,16</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 187,68</t>
+          <t>1,79; 205,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 188,28</t>
+          <t>-1,94; 181,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-60,02; 53,52</t>
+          <t>-55,99; 58,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,88; 151,87</t>
+          <t>11,7; 147,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 80,97</t>
+          <t>-27,03; 70,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,47; -3,51</t>
+          <t>-77,38; -0,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,93; 130,69</t>
+          <t>20,67; 131,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 94,21</t>
+          <t>-0,89; 91,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,39; 3,88</t>
+          <t>-62,68; 5,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 0,24</t>
+          <t>-3,65; 0,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,12; -0,44</t>
+          <t>-4,28; -0,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,54; -0,94</t>
+          <t>-4,85; -1,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,26</t>
+          <t>-2,96; 1,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,24; -0,26</t>
+          <t>-4,2; -0,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,12; -1,5</t>
+          <t>-5,14; -1,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,28</t>
+          <t>-2,59; 0,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; -0,8</t>
+          <t>-3,68; -0,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; -1,63</t>
+          <t>-4,18; -1,57</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-53,06; 6,26</t>
+          <t>-54,07; 6,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-61,66; -7,99</t>
+          <t>-62,07; -9,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-68,04; -17,76</t>
+          <t>-70,72; -18,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,47; 27,62</t>
+          <t>-41,63; 27,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,82; -3,75</t>
+          <t>-57,83; -4,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,09; -27,62</t>
+          <t>-69,56; -27,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,39; 5,92</t>
+          <t>-38,88; 6,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,19; -15,14</t>
+          <t>-54,59; -15,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-64,03; -31,11</t>
+          <t>-63,87; -30,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,0</t>
+          <t>-1,14; 1,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,51</t>
+          <t>-1,57; 0,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,56; -1,52</t>
+          <t>-3,59; -1,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,47</t>
+          <t>-0,96; 1,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,64; -0,34</t>
+          <t>-2,47; -0,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -2,45</t>
+          <t>-4,59; -2,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,88</t>
+          <t>-0,72; 0,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,7; -0,2</t>
+          <t>-1,77; -0,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -2,27</t>
+          <t>-3,76; -2,31</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 23,47</t>
+          <t>-20,63; 24,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 11,96</t>
+          <t>-29,48; 14,64</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-66,75; -33,6</t>
+          <t>-67,27; -36,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 27,22</t>
+          <t>-14,14; 24,01</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,62; -5,81</t>
+          <t>-38,07; -4,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-68,98; -44,91</t>
+          <t>-69,3; -45,29</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 17,79</t>
+          <t>-12,29; 17,9</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,5; -3,99</t>
+          <t>-30,23; -4,76</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-64,78; -45,72</t>
+          <t>-65,2; -45,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,85</t>
+          <t>-1,92</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,73</t>
+          <t>-3,44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,79</t>
+          <t>-2,68</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,35</t>
+          <t>-1,08; 3,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 3,62</t>
+          <t>-1,05; 3,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,11</t>
+          <t>-3,67; 0,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,28</t>
+          <t>-3,2; 1,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,85</t>
+          <t>-3,43; 1,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; -1,95</t>
+          <t>-5,57; -1,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,54</t>
+          <t>-1,52; 1,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,65</t>
+          <t>-1,49; 1,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,26; -1,28</t>
+          <t>-4,07; -1,24</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-52,51%</t>
+          <t>-54,65%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-70,12%</t>
+          <t>-64,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-63,16%</t>
+          <t>-60,57%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 134,47</t>
+          <t>-24,12; 140,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 139,41</t>
+          <t>-24,03; 144,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,1; 71,34</t>
+          <t>-84,55; 37,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,08; 34,15</t>
+          <t>-52,32; 32,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,4; 22,24</t>
+          <t>-54,37; 33,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,77; -44,59</t>
+          <t>-81,12; -38,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,04; 42,7</t>
+          <t>-29,22; 44,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 47,07</t>
+          <t>-28,34; 47,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-80,11; -23,92</t>
+          <t>-78,47; -31,99</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-4,14</t>
+          <t>-3,21</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,38</t>
+          <t>-4,15</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,28</t>
+          <t>-3,68</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 0,71</t>
+          <t>-3,25; 0,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -0,26</t>
+          <t>-4,28; -0,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,54; -2,37</t>
+          <t>-5,21; -1,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,99</t>
+          <t>-2,73; 1,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; -0,5</t>
+          <t>-4,75; -0,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; -2,56</t>
+          <t>-6,05; -2,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,61</t>
+          <t>-2,36; 0,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -0,75</t>
+          <t>-3,78; -0,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,64; -3,03</t>
+          <t>-5,01; -2,39</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-70,71%</t>
+          <t>-54,96%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-66,86%</t>
+          <t>-63,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-69,09%</t>
+          <t>-59,43%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,76; 16,69</t>
+          <t>-45,99; 20,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,29; -6,51</t>
+          <t>-61,58; -2,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-87,47; -46,58</t>
+          <t>-72,48; -22,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,75; 39,09</t>
+          <t>-35,81; 34,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,42; -9,03</t>
+          <t>-59,15; -4,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-80,43; -45,64</t>
+          <t>-76,22; -43,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 11,22</t>
+          <t>-34,05; 13,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,03; -12,97</t>
+          <t>-54,14; -14,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-80,99; -54,89</t>
+          <t>-71,72; -43,64</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,65</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>-0,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,87</t>
+          <t>0,11; 4,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 4,78</t>
+          <t>-0,16; 4,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,34</t>
+          <t>-2,25; 1,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,51</t>
+          <t>1,1; 6,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 3,26</t>
+          <t>-1,55; 3,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; -0,09</t>
+          <t>-2,94; 2,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,97</t>
+          <t>1,15; 4,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,44</t>
+          <t>-0,11; 3,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,16</t>
+          <t>-1,84; 1,35</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-18,18%</t>
+          <t>-1,34%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-47,24%</t>
+          <t>-5,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-35,92%</t>
+          <t>-4,1%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,79; 205,0</t>
+          <t>0,94; 178,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 181,43</t>
+          <t>-5,24; 182,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-55,99; 58,59</t>
+          <t>-45,82; 81,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,7; 147,8</t>
+          <t>13,13; 142,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,03; 70,56</t>
+          <t>-22,74; 73,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,38; -0,71</t>
+          <t>-42,87; 48,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,67; 131,55</t>
+          <t>18,82; 122,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 91,33</t>
+          <t>-2,72; 89,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,68; 5,52</t>
+          <t>-34,25; 35,91</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,72</t>
+          <t>-2,57</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,18</t>
+          <t>-2,56</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-2,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 0,28</t>
+          <t>-3,5; 0,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,28; -0,44</t>
+          <t>-4,19; -0,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,85; -1,02</t>
+          <t>-4,4; -0,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,37</t>
+          <t>-2,59; 1,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; -0,26</t>
+          <t>-4,3; -0,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; -1,42</t>
+          <t>-4,45; -0,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,3</t>
+          <t>-2,53; 0,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,87</t>
+          <t>-3,61; -0,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,18; -1,57</t>
+          <t>-4,0; -1,26</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-48,55%</t>
+          <t>-45,83%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-52,13%</t>
+          <t>-42,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-50,49%</t>
+          <t>-43,72%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,07; 6,95</t>
+          <t>-53,09; 8,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-62,07; -9,73</t>
+          <t>-62,32; -6,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,72; -18,91</t>
+          <t>-65,73; -14,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,63; 27,43</t>
+          <t>-36,62; 28,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,83; -4,96</t>
+          <t>-59,7; -7,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,56; -27,71</t>
+          <t>-60,77; -15,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-38,88; 6,25</t>
+          <t>-37,94; 6,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,59; -15,99</t>
+          <t>-53,92; -18,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,87; -30,74</t>
+          <t>-58,99; -24,69</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,55</t>
+          <t>-2,07</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,49</t>
+          <t>-2,71</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,03</t>
+          <t>-2,39</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,06</t>
+          <t>-1,11; 0,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,57</t>
+          <t>-1,55; 0,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -1,57</t>
+          <t>-3,08; -1,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,3</t>
+          <t>-1,01; 1,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,47; -0,27</t>
+          <t>-2,47; -0,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,59; -2,45</t>
+          <t>-3,79; -1,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,88</t>
+          <t>-0,66; 0,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; -0,24</t>
+          <t>-1,72; -0,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,76; -2,31</t>
+          <t>-3,12; -1,68</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-52,91%</t>
+          <t>-42,89%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-58,53%</t>
+          <t>-45,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-56,03%</t>
+          <t>-44,22%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 24,66</t>
+          <t>-20,05; 24,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 14,64</t>
+          <t>-28,84; 13,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-67,27; -36,86</t>
+          <t>-57,29; -24,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 24,01</t>
+          <t>-15,36; 27,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-38,07; -4,82</t>
+          <t>-37,97; -7,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-69,3; -45,29</t>
+          <t>-56,91; -30,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 17,9</t>
+          <t>-11,46; 17,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-30,23; -4,76</t>
+          <t>-29,75; -3,53</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-65,2; -45,67</t>
+          <t>-53,59; -33,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
